--- a/arista/dist/20261028_Arista個股模型_v0.3.xlsx
+++ b/arista/dist/20261028_Arista個股模型_v0.3.xlsx
@@ -168,10 +168,12 @@
     <definedName function="false" hidden="false" name="RLO_27" vbProcedure="false">In!$D$24</definedName>
     <definedName function="false" hidden="false" name="RLO_28" vbProcedure="false">In!$D$25</definedName>
     <definedName function="false" hidden="false" name="RLO_29" vbProcedure="false">In!$D$26</definedName>
+    <definedName function="false" hidden="false" name="rm_factor" vbProcedure="false">Val!$B$162</definedName>
     <definedName function="false" hidden="false" name="sh_g" vbProcedure="false">In!$E$55</definedName>
     <definedName function="false" hidden="false" name="sh_g_hi" vbProcedure="false">In!$F$55</definedName>
     <definedName function="false" hidden="false" name="sh_g_lo" vbProcedure="false">In!$D$55</definedName>
     <definedName function="false" hidden="false" name="svc25" vbProcedure="false">In!$E$29</definedName>
+    <definedName function="false" hidden="false" name="tp_comp_adj" vbProcedure="false">Val!$B$163</definedName>
     <definedName function="false" hidden="false" name="tp_g" vbProcedure="false">In!$E$75</definedName>
     <definedName function="false" hidden="false" name="tp_gd" vbProcedure="false">In!$E$76</definedName>
     <definedName function="false" hidden="false" name="tp_r" vbProcedure="false">In!$E$74</definedName>
@@ -200,7 +202,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2097" uniqueCount="732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2154" uniqueCount="773">
   <si>
     <r>
       <rPr>
@@ -3336,26 +3338,140 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：目標價 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">US$99.5</t>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：最敏感的是份額與市場量：份額相對值降到 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.80</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.70 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2028 EPS −8.8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI scale-out </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">交換器市場 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×0.8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時 −</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7.9%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；情境 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
     </r>
     <r>
       <rPr>
@@ -3374,7 +3490,894 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">DCF 87.2</t>
+      <t xml:space="preserve">CY2028–29 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">顆數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×0.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2028 EPS 4.97</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，比情境 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.99 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">低 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17.1%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，營收在 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">見頂。追蹤 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3Q26 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">財報（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-11-03</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營收（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標至少 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">35 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億美元）與 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年指引。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">重點觀察 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：以歷史看不貴：現價 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ FY2028 EPS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">28.8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">31.3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">34.7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），在 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2016–2025 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年底 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">24%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">～</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">33% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分位；目標價偏低是因 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Comparable </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同業成長較低。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DCF </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">權重改 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時加權目標價 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">104.4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">94.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">±4.9%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）、折現率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">±1pt </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時 −</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.9%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+8.3%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，都不改變放空級距。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-29</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：加權目標價中的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Comparable </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改用相對倍數調整後的值（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Val </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">節：同業前瞻倍數中位數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本公司 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年相對同業的倍數比，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">前瞻倍數；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Andy 2026-10-27</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「照建議做」、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10-29 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資料取回）。「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Comparable </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標價（市場主流同業法）」維持不調整。重點觀察 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的第一句已改為公式；重點觀察 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
     </r>
     <r>
       <rPr>
@@ -3393,1463 +4396,35 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Comparable 111.7 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">各半），比現價 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">172.37</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-10-23</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）低 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">42.3%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，級距 −</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">25%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">～−</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">50%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Comparable </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">單獨為 −</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">35.2%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。主因是倍數不是 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">EPS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：本模型 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">個月後前瞻 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">EPS 5.53 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">比共識前瞻 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">EPS 4.65 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">高 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12.6%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（期間差約一年），但同業（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Cisco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Ciena</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Celestica</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HPE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Credo</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）前瞻 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">P/E </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中位數 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20.2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍，現價隱含 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">37.1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍、共識目標價 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">243.59 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">隱含 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">52.4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍（比同業高 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">159%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）；市場給 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Arista </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">的 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">乙太網路份額與高毛利溢價，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Comparable </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未計入。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DCF 87.2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">更低，因 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ROE </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">雖有 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">28.6%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">情境 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2028 EPS 5.51 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">幾乎不成長（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+0.8%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">重點觀察 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：最敏感的是份額與市場量：份額相對值降到 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.80</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.70 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">時 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2028 EPS −8.8%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI scale-out </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">交換器市場 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×0.8 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">時 −</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">7.9%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；情境 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CY2028–29 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">顆數 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×0.6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2028 EPS 4.97</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，比情境 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">的 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5.99 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">低 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">17.1%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，營收在 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2027 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">見頂。追蹤 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3Q26 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">財報（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-11-03</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）的 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營收（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">目標至少 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">35 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">億美元）與 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年指引。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">重點觀察 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：以歷史看不貴：現價 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">÷ FY2028 EPS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">為 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">28.8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">31.3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">34.7 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">），在 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2016–2025 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年底 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">P/E </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">的 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">24%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">33% </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">分位；目標價偏低是因 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Comparable </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">同業成長較低。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DCF </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">權重改 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.7 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">時加權目標價 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">104.4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">94.6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">±4.9%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）、折現率 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">±1pt </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">時 −</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5.9%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+8.3%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，都不改變放空級距。</t>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">與其他說明中的目標價與上檔空間數字為調整前撰寫，以 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Val </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頁為準。</t>
     </r>
   </si>
   <si>
@@ -27429,6 +27004,1182 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">個月目標價時偏高。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.5 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">相對倍數調整（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Comparable </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標倍數＝同業中位數 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本公司 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年相對同業的 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">比；</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Andy 2026-10-27 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">新增，放在本頁最後以免位移既有儲存格）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資料：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2017–2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">各年度窗口（前一年 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月～當年 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月底前瞻 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）的中位數（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">tools/data/fwd_mult_hist.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Verified] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">來源、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Derived] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">彙總；有效值 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0 &lt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">值 ≤ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，無效值以「剔除</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」文字列示、不進中位數。本公司或同業有效年數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&lt; 7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不納入；有效同業 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&lt; 2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">家或本公司不足時係數＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（不調整）。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">公司</t>
+  </si>
+  <si>
+    <t xml:space="preserve">角色</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016/11–2017/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017/11–2018/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018/11–2019/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019/11–2020/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020/11–2021/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021/11–2022/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022/11–2023/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023/11–2024/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024/11–2025/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11–2026/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">有效年數</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年中位數</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">納入值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本公司</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg ANET US Equity BEST_PE_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">同業</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg CSCO US Equity BEST_PE_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg CIEN US Equity BEST_PE_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg CLS US Equity BEST_PE_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg HPE US Equity BEST_PE_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg CRDO US Equity BEST_PE_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本公司 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年中位數（納入值）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">空白＝本公司有效年數不足</t>
+  </si>
+  <si>
+    <t xml:space="preserve">納入的同業家數</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同業 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年中位數的中位數</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">原始比值（本公司 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同業）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝本公司長期比同業便宜（折價），＞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝長期溢價</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">夾值下限</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Assumed] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">避免單一歷史異常主導；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">tools/relative_multiple.py </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RM_LO</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">夾值上限</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Assumed] tools/relative_multiple.py </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RM_HI</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">相對倍數調整係數</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資料不足時＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（不調整）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Comparable </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標價（相對倍數調整後）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Comparable </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標價（市場主流同業法）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">調整係數；加權目標價使用本列</t>
     </r>
   </si>
   <si>
@@ -32357,7 +33108,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="13">
+  <numFmts count="14">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00%"/>
     <numFmt numFmtId="166" formatCode="#,##0.000"/>
@@ -32371,6 +33122,7 @@
     <numFmt numFmtId="174" formatCode="0%"/>
     <numFmt numFmtId="175" formatCode="@"/>
     <numFmt numFmtId="176" formatCode="#,##0"/>
+    <numFmt numFmtId="177" formatCode="0"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -32493,7 +33245,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -32639,6 +33391,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -32894,7 +33650,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="170"/>
@@ -32992,21 +33748,27 @@
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="str">
         <f aca="false">"投資建議："&amp;Val!B53&amp;"（依上檔空間固定規則）"</f>
-        <v>投資建議：放空（依上檔空間固定規則）</v>
+        <v>投資建議：中立（依上檔空間固定規則）</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
-        <v>16</v>
+      <c r="A21" s="0" t="str">
+        <f aca="false">"重點觀察 1：目標價 US$"&amp;TEXT(Val!$B$40,"#,##0.00")&amp;"（DCF "&amp;TEXT(Val!$B$23,"#,##0.00")&amp;"、Comparable（相對倍數調整後）"&amp;TEXT(tp_comp_adj,"#,##0.00")&amp;"；DCF 權重 "&amp;TEXT(tp_w_dcf,"0%")&amp;"），比現價 "&amp;TEXT(px,"#,##0.00")&amp;"（2026-10-23）"&amp;IF(Val!$B$43&gt;=0,"高 "&amp;TEXT(Val!$B$43,"0.0%"),"低 "&amp;TEXT(-Val!$B$43,"0.0%"))&amp;"，級距 "&amp;Val!$B$52&amp;"、投資建議 "&amp;Val!$B$53&amp;"。相對倍數調整係數 "&amp;TEXT(rm_factor,"0.00")&amp;"（本公司 10 年前瞻倍數中位數 ÷ 同業的中位數，夾在 0.5–2.0；Val 第 0.5 節），調整前加權上檔空間 "&amp;TEXT((tp_w_dcf*Val!$B$23+(1-tp_w_dcf)*Val!$B$36)/px-1,"+0.0%;−0.0%")&amp;"；Comparable 單獨（市場主流同業法、未調整）為 "&amp;TEXT(Val!$B$44,"+0.0%;−0.0%")&amp;"。"&amp;"以下為 2026-10-29 相對倍數調整前撰寫的說明，其中數字為調整前：主因是倍數不是 EPS：本模型 12 個月後前瞻 EPS 5.53 比共識前瞻 EPS 4.65 高 12.6%（期間差約一年），但同業（Cisco、Ciena、Celestica、HPE、Credo）前瞻 P/E 中位數 20.2 倍，現價隱含 37.1 倍、共識目標價 243.59 隱含 52.4 倍（比同業高 159%"&amp;"）；市場給 Arista 的 AI 乙太網路份額與高毛利溢價，Comparable 未計入。DCF 87.2 更低，因 ROE 雖有 28.6%，B 情境 FY2028 EPS 5.51 幾乎不成長（+0.8%）。"</f>
+        <v>重點觀察 1：目標價 US$155.30（DCF 87.24、Comparable（相對倍數調整後）223.36；DCF 權重 50%），比現價 172.37（2026-10-23）低 9.9%，級距 0%～−25%、投資建議 中立。相對倍數調整係數 2.00（本公司 10 年前瞻倍數中位數 ÷ 同業的中位數，夾在 0.5–2.0；Val 第 0.5 節），調整前加權上檔空間 −42.3%；Comparable 單獨（市場主流同業法、未調整）為 −35.2%。以下為 2026-10-29 相對倍數調整前撰寫的說明，其中數字為調整前：主因是倍數不是 EPS：本模型 12 個月後前瞻 EPS 5.53 比共識前瞻 EPS 4.65 高 12.6%（期間差約一年），但同業（Cisco、Ciena、Celestica、HPE、Credo）前瞻 P/E 中位數 20.2 倍，現價隱含 37.1 倍、共識目標價 243.59 隱含 52.4 倍（比同業高 159%）；市場給 Arista 的 AI 乙太網路份額與高毛利溢價，Comparable 未計入。DCF 87.2 更低，因 ROE 雖有 28.6%，B 情境 FY2028 EPS 5.51 幾乎不成長（+0.8%）。</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
         <v>18</v>
       </c>
     </row>
@@ -40188,7 +40950,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H143"/>
+  <dimension ref="A1:Q163"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
@@ -40781,8 +41543,8 @@
         <v>480</v>
       </c>
       <c r="B40" s="27" t="n">
-        <f aca="false">tp_w_dcf*B23+(1-tp_w_dcf)*B36</f>
-        <v>99.4630381559788</v>
+        <f aca="false">tp_w_dcf*B23+(1-tp_w_dcf)*tp_comp_adj</f>
+        <v>155.303628041274</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
@@ -40818,7 +41580,7 @@
       </c>
       <c r="B43" s="16" t="n">
         <f aca="false">B40/px-1</f>
-        <v>-0.422967812519703</v>
+        <v>-0.0990101059275184</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40942,7 +41704,7 @@
       </c>
       <c r="B52" s="32" t="str">
         <f aca="false">IF(B43&gt;0.5,"大於 50%",IF(B43&gt;0.25,"25%–50%",IF(B43&gt;=0,"0%–25%",IF(B43&gt;=-0.25,"0%～−25%",IF(B43&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v>−25%～−50%</v>
+        <v>0%～−25%</v>
       </c>
       <c r="E52" s="5" t="s">
         <v>499</v>
@@ -40954,7 +41716,7 @@
       </c>
       <c r="B53" s="32" t="str">
         <f aca="false">IF(B43&gt;0.5,"強力買進",IF(B43&gt;0.25,"買進",IF(B43&gt;=-0.25,"中立",IF(B43&gt;=-0.5,"放空","強力放空"))))</f>
-        <v>放空</v>
+        <v>中立</v>
       </c>
       <c r="E53" s="5" t="s">
         <v>501</v>
@@ -42029,6 +42791,478 @@
       </c>
       <c r="B143" s="0" t="s">
         <v>589</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="1" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="5" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="D148" s="13" t="s">
+        <v>594</v>
+      </c>
+      <c r="E148" s="13" t="s">
+        <v>595</v>
+      </c>
+      <c r="F148" s="13" t="s">
+        <v>596</v>
+      </c>
+      <c r="G148" s="13" t="s">
+        <v>597</v>
+      </c>
+      <c r="H148" s="13" t="s">
+        <v>598</v>
+      </c>
+      <c r="I148" s="13" t="s">
+        <v>599</v>
+      </c>
+      <c r="J148" s="13" t="s">
+        <v>600</v>
+      </c>
+      <c r="K148" s="13" t="s">
+        <v>601</v>
+      </c>
+      <c r="L148" s="13" t="s">
+        <v>602</v>
+      </c>
+      <c r="M148" s="13" t="s">
+        <v>603</v>
+      </c>
+      <c r="N148" s="6" t="s">
+        <v>604</v>
+      </c>
+      <c r="O148" s="13" t="s">
+        <v>605</v>
+      </c>
+      <c r="P148" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q148" s="6" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="0" t="s">
+        <v>607</v>
+      </c>
+      <c r="B149" s="0" t="s">
+        <v>608</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="D149" s="18" t="n">
+        <v>33.8415</v>
+      </c>
+      <c r="E149" s="18" t="n">
+        <v>36.0395</v>
+      </c>
+      <c r="F149" s="18" t="n">
+        <v>25.549</v>
+      </c>
+      <c r="G149" s="18" t="n">
+        <v>23.381</v>
+      </c>
+      <c r="H149" s="18" t="n">
+        <v>30.371</v>
+      </c>
+      <c r="I149" s="18" t="n">
+        <v>29.6845</v>
+      </c>
+      <c r="J149" s="18" t="n">
+        <v>26.6185</v>
+      </c>
+      <c r="K149" s="18" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="L149" s="18" t="n">
+        <v>42.7395</v>
+      </c>
+      <c r="M149" s="18" t="n">
+        <v>40.689</v>
+      </c>
+      <c r="N149" s="8" t="n">
+        <f aca="false">COUNT(D149:M149)</f>
+        <v>10</v>
+      </c>
+      <c r="O149" s="19" t="n">
+        <f aca="false">IF(N149&gt;0,MEDIAN(D149:M149),"")</f>
+        <v>32.10625</v>
+      </c>
+      <c r="P149" s="19" t="n">
+        <f aca="false">IF(N149&gt;=7,O149,"")</f>
+        <v>32.10625</v>
+      </c>
+      <c r="Q149" s="8" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="0" t="s">
+        <v>455</v>
+      </c>
+      <c r="B150" s="0" t="s">
+        <v>456</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="D150" s="18" t="n">
+        <v>13.032</v>
+      </c>
+      <c r="E150" s="18" t="n">
+        <v>15.3695</v>
+      </c>
+      <c r="F150" s="18" t="n">
+        <v>15.376</v>
+      </c>
+      <c r="G150" s="18" t="n">
+        <v>13.724</v>
+      </c>
+      <c r="H150" s="18" t="n">
+        <v>15.5665</v>
+      </c>
+      <c r="I150" s="18" t="n">
+        <v>13.072</v>
+      </c>
+      <c r="J150" s="18" t="n">
+        <v>12.9345</v>
+      </c>
+      <c r="K150" s="18" t="n">
+        <v>13.1135</v>
+      </c>
+      <c r="L150" s="18" t="n">
+        <v>16.21</v>
+      </c>
+      <c r="M150" s="18" t="n">
+        <v>20.714</v>
+      </c>
+      <c r="N150" s="8" t="n">
+        <f aca="false">COUNT(D150:M150)</f>
+        <v>10</v>
+      </c>
+      <c r="O150" s="19" t="n">
+        <f aca="false">IF(N150&gt;0,MEDIAN(D150:M150),"")</f>
+        <v>14.54675</v>
+      </c>
+      <c r="P150" s="19" t="n">
+        <f aca="false">IF(N150&gt;=7,O150,"")</f>
+        <v>14.54675</v>
+      </c>
+      <c r="Q150" s="8" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="0" t="s">
+        <v>460</v>
+      </c>
+      <c r="B151" s="0" t="s">
+        <v>461</v>
+      </c>
+      <c r="C151" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="D151" s="18" t="n">
+        <v>12.6425</v>
+      </c>
+      <c r="E151" s="18" t="n">
+        <v>16.492</v>
+      </c>
+      <c r="F151" s="18" t="n">
+        <v>18.083</v>
+      </c>
+      <c r="G151" s="18" t="n">
+        <v>15.489</v>
+      </c>
+      <c r="H151" s="18" t="n">
+        <v>18.2355</v>
+      </c>
+      <c r="I151" s="18" t="n">
+        <v>17.8225</v>
+      </c>
+      <c r="J151" s="18" t="n">
+        <v>15.194</v>
+      </c>
+      <c r="K151" s="18" t="n">
+        <v>18.4685</v>
+      </c>
+      <c r="L151" s="18" t="n">
+        <v>29.6055</v>
+      </c>
+      <c r="M151" s="18" t="n">
+        <v>45.5975</v>
+      </c>
+      <c r="N151" s="8" t="n">
+        <f aca="false">COUNT(D151:M151)</f>
+        <v>10</v>
+      </c>
+      <c r="O151" s="19" t="n">
+        <f aca="false">IF(N151&gt;0,MEDIAN(D151:M151),"")</f>
+        <v>17.95275</v>
+      </c>
+      <c r="P151" s="19" t="n">
+        <f aca="false">IF(N151&gt;=7,O151,"")</f>
+        <v>17.95275</v>
+      </c>
+      <c r="Q151" s="8" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="0" t="s">
+        <v>463</v>
+      </c>
+      <c r="B152" s="0" t="s">
+        <v>464</v>
+      </c>
+      <c r="C152" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="D152" s="18" t="n">
+        <v>9.973</v>
+      </c>
+      <c r="E152" s="18" t="n">
+        <v>9.182</v>
+      </c>
+      <c r="F152" s="18" t="n">
+        <v>8.5745</v>
+      </c>
+      <c r="G152" s="18" t="n">
+        <v>9.38</v>
+      </c>
+      <c r="H152" s="18" t="n">
+        <v>7.8455</v>
+      </c>
+      <c r="I152" s="18" t="n">
+        <v>6.496</v>
+      </c>
+      <c r="J152" s="18" t="n">
+        <v>6.4765</v>
+      </c>
+      <c r="K152" s="18" t="n">
+        <v>13.3505</v>
+      </c>
+      <c r="L152" s="18" t="n">
+        <v>23.4305</v>
+      </c>
+      <c r="M152" s="18" t="n">
+        <v>28.9945</v>
+      </c>
+      <c r="N152" s="8" t="n">
+        <f aca="false">COUNT(D152:M152)</f>
+        <v>10</v>
+      </c>
+      <c r="O152" s="19" t="n">
+        <f aca="false">IF(N152&gt;0,MEDIAN(D152:M152),"")</f>
+        <v>9.281</v>
+      </c>
+      <c r="P152" s="19" t="n">
+        <f aca="false">IF(N152&gt;=7,O152,"")</f>
+        <v>9.281</v>
+      </c>
+      <c r="Q152" s="8" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="0" t="s">
+        <v>465</v>
+      </c>
+      <c r="B153" s="0" t="s">
+        <v>466</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="D153" s="18" t="n">
+        <v>9.8045</v>
+      </c>
+      <c r="E153" s="18" t="n">
+        <v>11.116</v>
+      </c>
+      <c r="F153" s="18" t="n">
+        <v>8.738</v>
+      </c>
+      <c r="G153" s="18" t="n">
+        <v>6.9755</v>
+      </c>
+      <c r="H153" s="18" t="n">
+        <v>7.5105</v>
+      </c>
+      <c r="I153" s="18" t="n">
+        <v>7.108</v>
+      </c>
+      <c r="J153" s="18" t="n">
+        <v>7.8275</v>
+      </c>
+      <c r="K153" s="18" t="n">
+        <v>8.972</v>
+      </c>
+      <c r="L153" s="18" t="n">
+        <v>9.945</v>
+      </c>
+      <c r="M153" s="18" t="n">
+        <v>11.4715</v>
+      </c>
+      <c r="N153" s="8" t="n">
+        <f aca="false">COUNT(D153:M153)</f>
+        <v>10</v>
+      </c>
+      <c r="O153" s="19" t="n">
+        <f aca="false">IF(N153&gt;0,MEDIAN(D153:M153),"")</f>
+        <v>8.855</v>
+      </c>
+      <c r="P153" s="19" t="n">
+        <f aca="false">IF(N153&gt;=7,O153,"")</f>
+        <v>8.855</v>
+      </c>
+      <c r="Q153" s="8" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="0" t="s">
+        <v>467</v>
+      </c>
+      <c r="B154" s="0" t="s">
+        <v>468</v>
+      </c>
+      <c r="C154" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="I154" s="18" t="n">
+        <v>59.289</v>
+      </c>
+      <c r="J154" s="18" t="n">
+        <v>66.363</v>
+      </c>
+      <c r="K154" s="18" t="n">
+        <v>70.005</v>
+      </c>
+      <c r="L154" s="18" t="n">
+        <v>64.678</v>
+      </c>
+      <c r="M154" s="18" t="n">
+        <v>32.985</v>
+      </c>
+      <c r="N154" s="8" t="n">
+        <f aca="false">COUNT(D154:M154)</f>
+        <v>5</v>
+      </c>
+      <c r="O154" s="19" t="n">
+        <f aca="false">IF(N154&gt;0,MEDIAN(D154:M154),"")</f>
+        <v>64.678</v>
+      </c>
+      <c r="P154" s="19" t="str">
+        <f aca="false">IF(N154&gt;=7,O154,"")</f>
+        <v/>
+      </c>
+      <c r="Q154" s="8" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="5" t="s">
+        <v>617</v>
+      </c>
+      <c r="B156" s="19" t="n">
+        <f aca="false">P149</f>
+        <v>32.10625</v>
+      </c>
+      <c r="E156" s="5" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="5" t="s">
+        <v>619</v>
+      </c>
+      <c r="B157" s="37" t="n">
+        <f aca="false">COUNT(P150:P154)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="5" t="s">
+        <v>620</v>
+      </c>
+      <c r="B158" s="19" t="n">
+        <f aca="false">IF(B157&gt;0,MEDIAN(P150:P154),"")</f>
+        <v>11.913875</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="5" t="s">
+        <v>621</v>
+      </c>
+      <c r="B159" s="19" t="n">
+        <f aca="false">IF(AND(ISNUMBER(B156),B157&gt;=2),B156/B158,"")</f>
+        <v>2.69486208307541</v>
+      </c>
+      <c r="E159" s="5" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="5" t="s">
+        <v>623</v>
+      </c>
+      <c r="B160" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E160" s="8" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="B161" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E161" s="8" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="B162" s="33" t="n">
+        <f aca="false">IF(ISNUMBER(B159),MIN(MAX(B159,B160),B161),1)</f>
+        <v>2</v>
+      </c>
+      <c r="E162" s="5" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="B163" s="27" t="n">
+        <f aca="false">Val!$B$36*B162</f>
+        <v>223.362359541179</v>
+      </c>
+      <c r="E163" s="5" t="s">
+        <v>630</v>
       </c>
     </row>
   </sheetData>
@@ -42058,7 +43292,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>590</v>
+        <v>631</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42066,28 +43300,28 @@
         <v>22</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>591</v>
+        <v>632</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>592</v>
+        <v>633</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>593</v>
+        <v>634</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>594</v>
+        <v>635</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>595</v>
+        <v>636</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>596</v>
+        <v>637</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>597</v>
+        <v>638</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>598</v>
+        <v>639</v>
       </c>
       <c r="J3" s="6" t="s">
         <v>331</v>
@@ -42095,12 +43329,12 @@
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>599</v>
+        <v>640</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>600</v>
+        <v>641</v>
       </c>
       <c r="B5" s="21" t="n">
         <f aca="false">cons_rev26</f>
@@ -42134,12 +43368,12 @@
         <v>225</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>601</v>
+        <v>642</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>602</v>
+        <v>643</v>
       </c>
       <c r="B6" s="21" t="n">
         <f aca="false">cons_eps26</f>
@@ -42173,12 +43407,12 @@
         <v>225</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>603</v>
+        <v>644</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>604</v>
+        <v>645</v>
       </c>
       <c r="B7" s="21" t="n">
         <f aca="false">erste_eps27</f>
@@ -42209,15 +43443,15 @@
         <v>0.140954753251673</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>605</v>
+        <v>646</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>606</v>
+        <v>647</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>607</v>
+        <v>648</v>
       </c>
       <c r="B8" s="21" t="n">
         <f aca="false">px/pe_fwd_sa</f>
@@ -42248,15 +43482,15 @@
         <v>0.175026520362467</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>608</v>
+        <v>649</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>609</v>
+        <v>650</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>610</v>
+        <v>651</v>
       </c>
       <c r="C9" s="16" t="n">
         <f aca="false">PL!E77</f>
@@ -42276,12 +43510,12 @@
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>611</v>
+        <v>652</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>612</v>
+        <v>653</v>
       </c>
       <c r="B11" s="16" t="n">
         <f aca="false">idc_anet</f>
@@ -42312,15 +43546,15 @@
         <v>-0.0414936013561196</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>613</v>
+        <v>654</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>614</v>
+        <v>655</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>615</v>
+        <v>656</v>
       </c>
       <c r="B12" s="16" t="n">
         <f aca="false">1-dell_top2</f>
@@ -42351,15 +43585,15 @@
         <v>-0.35449360135612</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>616</v>
+        <v>657</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>617</v>
+        <v>658</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>618</v>
+        <v>659</v>
       </c>
       <c r="B13" s="16" t="n">
         <v>0.54</v>
@@ -42389,12 +43623,12 @@
         <v>-0.137074524943843</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>619</v>
+        <v>660</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>620</v>
+        <v>661</v>
       </c>
       <c r="C14" s="12" t="n">
         <f aca="false">PL!E69/itc_27</f>
@@ -42409,15 +43643,15 @@
         <v>0.00431537761809352</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>621</v>
+        <v>662</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>622</v>
+        <v>663</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>623</v>
+        <v>664</v>
       </c>
       <c r="C15" s="16" t="n">
         <f aca="false">PL!F68</f>
@@ -42437,12 +43671,12 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>624</v>
+        <v>665</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>625</v>
+        <v>666</v>
       </c>
       <c r="C17" s="16" t="n">
         <f aca="false">PL!D80</f>
@@ -42457,15 +43691,15 @@
         <v>0.646666666666667</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>626</v>
+        <v>667</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>627</v>
+        <v>668</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>628</v>
+        <v>669</v>
       </c>
       <c r="B18" s="16" t="n">
         <f aca="false">a26_gp/a26_rev</f>
@@ -42496,10 +43730,10 @@
         <v>-0.00750886183670274</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>629</v>
+        <v>670</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>630</v>
+        <v>671</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42534,20 +43768,20 @@
         <v>0.000515958108592507</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>631</v>
+        <v>672</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>632</v>
+        <v>673</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>633</v>
+        <v>674</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>634</v>
+        <v>675</v>
       </c>
     </row>
   </sheetData>
@@ -42576,53 +43810,53 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>635</v>
+        <v>676</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>636</v>
+        <v>677</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>637</v>
+        <v>678</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>638</v>
+        <v>679</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>639</v>
+        <v>680</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>640</v>
+        <v>681</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>534</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>641</v>
+        <v>682</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>642</v>
+        <v>683</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>643</v>
+        <v>684</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>644</v>
+        <v>685</v>
       </c>
       <c r="K3" s="13" t="s">
         <v>536</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>645</v>
+        <v>686</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>646</v>
+        <v>687</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>647</v>
+        <v>688</v>
       </c>
       <c r="C4" s="21" t="n">
         <f aca="false">PL!E72</f>
@@ -42667,10 +43901,10 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>648</v>
+        <v>689</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>649</v>
+        <v>690</v>
       </c>
       <c r="C5" s="21" t="n">
         <f aca="false">E52</f>
@@ -42715,10 +43949,10 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>650</v>
+        <v>691</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>651</v>
+        <v>692</v>
       </c>
       <c r="C6" s="21" t="n">
         <f aca="false">E87</f>
@@ -42763,10 +43997,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>652</v>
+        <v>693</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>653</v>
+        <v>694</v>
       </c>
       <c r="C7" s="21" t="n">
         <f aca="false">E122</f>
@@ -42811,10 +44045,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>654</v>
+        <v>695</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>655</v>
+        <v>696</v>
       </c>
       <c r="C8" s="21" t="n">
         <f aca="false">E157</f>
@@ -42859,10 +44093,10 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>656</v>
+        <v>697</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>657</v>
+        <v>698</v>
       </c>
       <c r="C9" s="21" t="n">
         <f aca="false">E192</f>
@@ -42907,10 +44141,10 @@
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>658</v>
+        <v>699</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>659</v>
+        <v>700</v>
       </c>
       <c r="C10" s="21" t="n">
         <f aca="false">E227</f>
@@ -42955,10 +44189,10 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>660</v>
+        <v>701</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>661</v>
+        <v>702</v>
       </c>
       <c r="C11" s="21" t="n">
         <f aca="false">E262</f>
@@ -43003,10 +44237,10 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>662</v>
+        <v>703</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>663</v>
+        <v>704</v>
       </c>
       <c r="C12" s="21" t="n">
         <f aca="false">E297</f>
@@ -43051,10 +44285,10 @@
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>664</v>
+        <v>705</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>665</v>
+        <v>706</v>
       </c>
       <c r="C13" s="21" t="n">
         <f aca="false">E332</f>
@@ -43099,10 +44333,10 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>666</v>
+        <v>707</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>667</v>
+        <v>708</v>
       </c>
       <c r="C14" s="21" t="n">
         <f aca="false">E367</f>
@@ -43147,10 +44381,10 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>668</v>
+        <v>709</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>669</v>
+        <v>710</v>
       </c>
       <c r="C15" s="21" t="n">
         <f aca="false">E402</f>
@@ -43195,10 +44429,10 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>670</v>
+        <v>711</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>671</v>
+        <v>712</v>
       </c>
       <c r="C16" s="21" t="n">
         <f aca="false">PL!E107</f>
@@ -43243,10 +44477,10 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>672</v>
+        <v>713</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>673</v>
+        <v>714</v>
       </c>
       <c r="C17" s="21" t="n">
         <f aca="false">PL!E142</f>
@@ -43291,124 +44525,124 @@
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>674</v>
+        <v>715</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>675</v>
+        <v>716</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>676</v>
+        <v>717</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>677</v>
+        <v>718</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>678</v>
+        <v>719</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>679</v>
+        <v>720</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>680</v>
+        <v>721</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>681</v>
+        <v>722</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>682</v>
+        <v>723</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>683</v>
+        <v>724</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>684</v>
+        <v>725</v>
       </c>
       <c r="C23" s="21" t="n">
-        <f aca="false">tp_w_dcf*(tp_wA*(MAX(0,Val!B7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$7+Val!B8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$8+Val!B9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$9+Val!B10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$10+Val!B11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$11+Val!B12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$12+Val!B12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^Val!$F$12))+tp_wB*(MAX(0,Val!C7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$7+Val!C8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$8+Val!C9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$9+Val!C10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$10+Val!C11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$11+Val!C12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$12+Val!C12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^Val!$F$12))+tp_wC*(MAX(0,Val!D7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$7+Val!D8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$8+Val!D9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$9+Val!D10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$10+Val!D11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$11+Val!D12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$12+Val!D12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^Val!$F$12)))*(1+(tp_r-0.01))+(1-tp_w_dcf)*Val!$B$36</f>
-        <v>107.702830186988</v>
+        <f aca="false">tp_w_dcf*(tp_wA*(MAX(0,Val!B7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$7+Val!B8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$8+Val!B9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$9+Val!B10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$10+Val!B11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$11+Val!B12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$12+Val!B12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^Val!$F$12))+tp_wB*(MAX(0,Val!C7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$7+Val!C8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$8+Val!C9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$9+Val!C10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$10+Val!C11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$11+Val!C12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$12+Val!C12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^Val!$F$12))+tp_wC*(MAX(0,Val!D7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$7+Val!D8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$8+Val!D9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$9+Val!D10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$10+Val!D11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$11+Val!D12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$12+Val!D12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^Val!$F$12)))*(1+(tp_r-0.01))+(1-tp_w_dcf)*tp_comp_adj</f>
+        <v>163.543420072283</v>
       </c>
       <c r="D23" s="16" t="n">
         <f aca="false">C23/G23-1</f>
-        <v>0.0828427542911754</v>
+        <v>0.0530560176534942</v>
       </c>
       <c r="E23" s="21" t="n">
-        <f aca="false">tp_w_dcf*(tp_wA*(MAX(0,Val!B7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$7+Val!B8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$8+Val!B9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$9+Val!B10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$10+Val!B11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$11+Val!B12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$12+Val!B12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^Val!$F$12))+tp_wB*(MAX(0,Val!C7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$7+Val!C8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$8+Val!C9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$9+Val!C10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$10+Val!C11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$11+Val!C12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$12+Val!C12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^Val!$F$12))+tp_wC*(MAX(0,Val!D7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$7+Val!D8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$8+Val!D9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$9+Val!D10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$10+Val!D11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$11+Val!D12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$12+Val!D12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^Val!$F$12)))*(1+(tp_r+0.01))+(1-tp_w_dcf)*Val!$B$36</f>
-        <v>93.5764815685177</v>
+        <f aca="false">tp_w_dcf*(tp_wA*(MAX(0,Val!B7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$7+Val!B8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$8+Val!B9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$9+Val!B10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$10+Val!B11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$11+Val!B12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$12+Val!B12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^Val!$F$12))+tp_wB*(MAX(0,Val!C7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$7+Val!C8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$8+Val!C9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$9+Val!C10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$10+Val!C11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$11+Val!C12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$12+Val!C12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^Val!$F$12))+tp_wC*(MAX(0,Val!D7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$7+Val!D8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$8+Val!D9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$9+Val!D10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$10+Val!D11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$11+Val!D12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$12+Val!D12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^Val!$F$12)))*(1+(tp_r+0.01))+(1-tp_w_dcf)*tp_comp_adj</f>
+        <v>149.417071453813</v>
       </c>
       <c r="F23" s="16" t="n">
         <f aca="false">E23/G23-1</f>
-        <v>-0.059183357924677</v>
+        <v>-0.0379035355561475</v>
       </c>
       <c r="G23" s="21" t="n">
         <f aca="false">Val!$B$40</f>
-        <v>99.4630381559788</v>
+        <v>155.303628041274</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>685</v>
+        <v>726</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>686</v>
+        <v>727</v>
       </c>
       <c r="C24" s="21" t="n">
-        <f aca="false">tp_w_dcf*(tp_wA*(MAX(0,Val!B7*Val!$G$7*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$7+Val!B8*Val!$G$8*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$8+Val!B9*Val!$G$9*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$9+Val!B10*Val!$G$10*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$10+Val!B11*Val!$G$11*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$11+Val!B12*Val!$G$12*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$12+Val!B12*(1-MIN(0.8,(tp_g-0.01)/tp_roe))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^Val!$F$12))+tp_wB*(MAX(0,Val!C7*Val!$G$7*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$7+Val!C8*Val!$G$8*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$8+Val!C9*Val!$G$9*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$9+Val!C10*Val!$G$10*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$10+Val!C11*Val!$G$11*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$11+Val!C12*Val!$G$12*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$12+Val!C12*(1-MIN(0.8,(tp_g-0.01)/tp_roe))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^Val!$F$12))+tp_wC*(MAX(0,Val!D7*Val!$G$7*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$7+Val!D8*Val!$G$8*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$8+Val!D9*Val!$G$9*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$9+Val!D10*Val!$G$10*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$10+Val!D11*Val!$G$11*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$11+Val!D12*Val!$G$12*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$12+Val!D12*(1-MIN(0.8,(tp_g-0.01)/tp_roe))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^Val!$F$12)))*(1+tp_r)+(1-tp_w_dcf)*Val!$B$36</f>
-        <v>96.3441624931583</v>
+        <f aca="false">tp_w_dcf*(tp_wA*(MAX(0,Val!B7*Val!$G$7*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$7+Val!B8*Val!$G$8*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$8+Val!B9*Val!$G$9*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$9+Val!B10*Val!$G$10*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$10+Val!B11*Val!$G$11*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$11+Val!B12*Val!$G$12*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$12+Val!B12*(1-MIN(0.8,(tp_g-0.01)/tp_roe))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^Val!$F$12))+tp_wB*(MAX(0,Val!C7*Val!$G$7*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$7+Val!C8*Val!$G$8*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$8+Val!C9*Val!$G$9*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$9+Val!C10*Val!$G$10*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$10+Val!C11*Val!$G$11*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$11+Val!C12*Val!$G$12*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$12+Val!C12*(1-MIN(0.8,(tp_g-0.01)/tp_roe))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^Val!$F$12))+tp_wC*(MAX(0,Val!D7*Val!$G$7*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$7+Val!D8*Val!$G$8*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$8+Val!D9*Val!$G$9*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$9+Val!D10*Val!$G$10*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$10+Val!D11*Val!$G$11*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$11+Val!D12*Val!$G$12*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$12+Val!D12*(1-MIN(0.8,(tp_g-0.01)/tp_roe))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^Val!$F$12)))*(1+tp_r)+(1-tp_w_dcf)*tp_comp_adj</f>
+        <v>152.184752378453</v>
       </c>
       <c r="D24" s="16" t="n">
         <f aca="false">C24/G24-1</f>
-        <v>-0.0313571324649211</v>
+        <v>-0.0200824391687209</v>
       </c>
       <c r="E24" s="21" t="n">
-        <f aca="false">tp_w_dcf*(tp_wA*(MAX(0,Val!B7*Val!$G$7*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$7+Val!B8*Val!$G$8*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$8+Val!B9*Val!$G$9*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$9+Val!B10*Val!$G$10*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$10+Val!B11*Val!$G$11*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$11+Val!B12*Val!$G$12*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$12+Val!B12*(1-MIN(0.8,(tp_g+0.01)/tp_roe))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^Val!$F$12))+tp_wB*(MAX(0,Val!C7*Val!$G$7*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$7+Val!C8*Val!$G$8*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$8+Val!C9*Val!$G$9*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$9+Val!C10*Val!$G$10*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$10+Val!C11*Val!$G$11*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$11+Val!C12*Val!$G$12*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$12+Val!C12*(1-MIN(0.8,(tp_g+0.01)/tp_roe))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^Val!$F$12))+tp_wC*(MAX(0,Val!D7*Val!$G$7*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$7+Val!D8*Val!$G$8*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$8+Val!D9*Val!$G$9*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$9+Val!D10*Val!$G$10*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$10+Val!D11*Val!$G$11*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$11+Val!D12*Val!$G$12*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$12+Val!D12*(1-MIN(0.8,(tp_g+0.01)/tp_roe))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^Val!$F$12)))*(1+tp_r)+(1-tp_w_dcf)*Val!$B$36</f>
-        <v>104.00369321932</v>
+        <f aca="false">tp_w_dcf*(tp_wA*(MAX(0,Val!B7*Val!$G$7*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$7+Val!B8*Val!$G$8*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$8+Val!B9*Val!$G$9*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$9+Val!B10*Val!$G$10*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$10+Val!B11*Val!$G$11*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$11+Val!B12*Val!$G$12*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$12+Val!B12*(1-MIN(0.8,(tp_g+0.01)/tp_roe))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^Val!$F$12))+tp_wB*(MAX(0,Val!C7*Val!$G$7*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$7+Val!C8*Val!$G$8*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$8+Val!C9*Val!$G$9*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$9+Val!C10*Val!$G$10*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$10+Val!C11*Val!$G$11*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$11+Val!C12*Val!$G$12*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$12+Val!C12*(1-MIN(0.8,(tp_g+0.01)/tp_roe))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^Val!$F$12))+tp_wC*(MAX(0,Val!D7*Val!$G$7*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$7+Val!D8*Val!$G$8*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$8+Val!D9*Val!$G$9*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$9+Val!D10*Val!$G$10*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$10+Val!D11*Val!$G$11*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$11+Val!D12*Val!$G$12*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$12+Val!D12*(1-MIN(0.8,(tp_g+0.01)/tp_roe))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^Val!$F$12)))*(1+tp_r)+(1-tp_w_dcf)*tp_comp_adj</f>
+        <v>159.844283104614</v>
       </c>
       <c r="F24" s="16" t="n">
         <f aca="false">E24/G24-1</f>
-        <v>0.0456516827509335</v>
+        <v>0.0292372761706121</v>
       </c>
       <c r="G24" s="21" t="n">
         <f aca="false">Val!$B$40</f>
-        <v>99.4630381559788</v>
+        <v>155.303628041274</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>687</v>
+        <v>728</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>688</v>
+        <v>729</v>
       </c>
       <c r="C25" s="21" t="n">
-        <f aca="false">0.3*(tp_wA*(MAX(0,Val!B7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$7+Val!B8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$8+Val!B9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$9+Val!B10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$10+Val!B11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$11+Val!B12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$12+Val!B12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^Val!$F$12))+tp_wB*(MAX(0,Val!C7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$7+Val!C8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$8+Val!C9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$9+Val!C10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$10+Val!C11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$11+Val!C12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$12+Val!C12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^Val!$F$12))+tp_wC*(MAX(0,Val!D7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$7+Val!D8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$8+Val!D9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$9+Val!D10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$10+Val!D11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$11+Val!D12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$12+Val!D12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^Val!$F$12)))*(1+tp_r)+(1-0.3)*Val!$B$36</f>
-        <v>104.350294801823</v>
+        <f aca="false">0.3*(tp_wA*(MAX(0,Val!B7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$7+Val!B8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$8+Val!B9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$9+Val!B10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$10+Val!B11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$11+Val!B12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$12+Val!B12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^Val!$F$12))+tp_wB*(MAX(0,Val!C7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$7+Val!C8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$8+Val!C9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$9+Val!C10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$10+Val!C11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$11+Val!C12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$12+Val!C12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^Val!$F$12))+tp_wC*(MAX(0,Val!D7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$7+Val!D8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$8+Val!D9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$9+Val!D10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$10+Val!D11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$11+Val!D12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$12+Val!D12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^Val!$F$12)))*(1+tp_r)+(1-0.3)*tp_comp_adj</f>
+        <v>182.527120641236</v>
       </c>
       <c r="D25" s="16" t="n">
         <f aca="false">C25/G25-1</f>
-        <v>0.0491364102329157</v>
+        <v>0.175292058165746</v>
       </c>
       <c r="E25" s="21" t="n">
-        <f aca="false">0.7*(tp_wA*(MAX(0,Val!B7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$7+Val!B8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$8+Val!B9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$9+Val!B10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$10+Val!B11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$11+Val!B12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$12+Val!B12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^Val!$F$12))+tp_wB*(MAX(0,Val!C7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$7+Val!C8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$8+Val!C9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$9+Val!C10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$10+Val!C11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$11+Val!C12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$12+Val!C12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^Val!$F$12))+tp_wC*(MAX(0,Val!D7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$7+Val!D8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$8+Val!D9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$9+Val!D10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$10+Val!D11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$11+Val!D12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$12+Val!D12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^Val!$F$12)))*(1+tp_r)+(1-0.7)*Val!$B$36</f>
-        <v>94.5757815101345</v>
+        <f aca="false">0.7*(tp_wA*(MAX(0,Val!B7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$7+Val!B8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$8+Val!B9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$9+Val!B10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$10+Val!B11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$11+Val!B12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$12+Val!B12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^Val!$F$12))+tp_wB*(MAX(0,Val!C7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$7+Val!C8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$8+Val!C9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$9+Val!C10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$10+Val!C11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$11+Val!C12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$12+Val!C12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^Val!$F$12))+tp_wC*(MAX(0,Val!D7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$7+Val!D8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$8+Val!D9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$9+Val!D10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$10+Val!D11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$11+Val!D12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$12+Val!D12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^Val!$F$12)))*(1+tp_r)+(1-0.7)*tp_comp_adj</f>
+        <v>128.080135441311</v>
       </c>
       <c r="F25" s="16" t="n">
         <f aca="false">E25/G25-1</f>
-        <v>-0.0491364102329158</v>
+        <v>-0.175292058165746</v>
       </c>
       <c r="G25" s="21" t="n">
         <f aca="false">Val!$B$40</f>
-        <v>99.4630381559788</v>
+        <v>155.303628041274</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>689</v>
+        <v>730</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44190,7 +45424,7 @@
     </row>
     <row r="75" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="s">
-        <v>690</v>
+        <v>731</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44972,7 +46206,7 @@
     </row>
     <row r="110" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="3" t="s">
-        <v>691</v>
+        <v>732</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45754,7 +46988,7 @@
     </row>
     <row r="145" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="3" t="s">
-        <v>692</v>
+        <v>733</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46536,7 +47770,7 @@
     </row>
     <row r="180" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="3" t="s">
-        <v>693</v>
+        <v>734</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47318,7 +48552,7 @@
     </row>
     <row r="215" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="3" t="s">
-        <v>694</v>
+        <v>735</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48100,7 +49334,7 @@
     </row>
     <row r="250" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="3" t="s">
-        <v>695</v>
+        <v>736</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48882,7 +50116,7 @@
     </row>
     <row r="285" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="3" t="s">
-        <v>696</v>
+        <v>737</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49664,7 +50898,7 @@
     </row>
     <row r="320" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="3" t="s">
-        <v>697</v>
+        <v>738</v>
       </c>
     </row>
     <row r="321" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50446,7 +51680,7 @@
     </row>
     <row r="355" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="3" t="s">
-        <v>698</v>
+        <v>739</v>
       </c>
     </row>
     <row r="356" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51228,7 +52462,7 @@
     </row>
     <row r="390" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="3" t="s">
-        <v>699</v>
+        <v>740</v>
       </c>
     </row>
     <row r="391" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52033,132 +53267,132 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>700</v>
+        <v>741</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>701</v>
+        <v>742</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>702</v>
+        <v>743</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>703</v>
+        <v>744</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>704</v>
+        <v>745</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>705</v>
+        <v>746</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>706</v>
+        <v>747</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>707</v>
+        <v>748</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>708</v>
+        <v>749</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>709</v>
+        <v>750</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>710</v>
+        <v>751</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>711</v>
+        <v>752</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>712</v>
+        <v>753</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>713</v>
+        <v>754</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>714</v>
+        <v>755</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>715</v>
+        <v>756</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>716</v>
+        <v>757</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>717</v>
+        <v>758</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>718</v>
+        <v>759</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>719</v>
+        <v>760</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>721</v>
+        <v>762</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>722</v>
+        <v>763</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>723</v>
+        <v>764</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>724</v>
+        <v>765</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>725</v>
+        <v>766</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>726</v>
+        <v>767</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>727</v>
+        <v>768</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>728</v>
+        <v>769</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>729</v>
+        <v>770</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>730</v>
+        <v>771</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>731</v>
+        <v>772</v>
       </c>
     </row>
   </sheetData>
